--- a/output/2026-10-03_19_Malesia_Perlis_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-03_19_Malesia_Perlis_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via fetch diretto sito ufficiale. Attivo dal 1986. Distributore ufficiale Linde Malaysia, rivenditore ESAB/Bosch/NTN/SMC. Indirizzo: 282 &amp; 284, Jalan Kangar-Alor Setar, Taman Mutiara, 01000 Kangar, Perlis. Distributore B2B confermato, non cliente finale. WhatsApp: 016-422 5570.</t>
+          <t>Verificato via fetch diretto sito ufficiale. Attivo dal 1986. Distributore ufficiale Linde Malaysia, rivenditore ESAB/Bosch/NTN/SMC. Indirizzo: 282 &amp; 284, Jalan Kangar-Alor Setar, Taman Mutiara, 01000 Kangar, Perlis. Distributore B2B confermato, non cliente finale. WhatsApp: 016-422 5570. [DUPLICATO — vedi anche: 2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>ProTool Works</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Arau, Perlis</t>
@@ -532,10 +531,9 @@
           <t>019-546 9064</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato tramite directory aziendale (Cybo/Google Business), dati coerenti su piu ricerche. Nessun sito proprio reperito. Indirizzo: 20, Jalan Tengku Budriah 3, Taman Tengku Budriah, 02600 Arau, Perlis.</t>
+          <t>Verificato tramite directory aziendale (Cybo/Google Business), dati coerenti su piu ricerche. Nessun sito proprio reperito. Indirizzo: 20, Jalan Tengku Budriah 3, Taman Tengku Budriah, 02600 Arau, Perlis. [DUPLICATO — vedi anche: 2026-10-03_18_Malesia_Perlis_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -550,7 +548,6 @@
           <t>Kdt Maju Enterprise</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Arau, Perlis</t>
@@ -561,11 +558,9 @@
           <t>Industrial equipment supply / welding supply store / generator shop</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato con riserva: esistenza confermata da directory, ma indirizzo preciso non determinabile (solo 'Arau, 02600'), telefono ed email non reperiti. Esiste sede omonima in Jalan Kampung Tengah segnalata permanently closed - possibile indirizzo obsoleto. Consigliata verifica telefonica diretta.</t>
+          <t>Verificato con riserva: esistenza confermata da directory, ma indirizzo preciso non determinabile (solo 'Arau, 02600'), telefono ed email non reperiti. Esiste sede omonima in Jalan Kampung Tengah segnalata permanently closed - possibile indirizzo obsoleto. Consigliata verifica telefonica diretta. [DUPLICATO — vedi anche: 2026-10-03_18_Malesia_Perlis_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
